--- a/data/trans_orig/IP07C13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C13-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28795</t>
+          <t>29289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41733</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48652</t>
+          <t>49346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66743</t>
+          <t>68225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>26845</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38938</t>
+          <t>37971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>23581</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37211</t>
+          <t>36243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54380</t>
+          <t>52100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72284</t>
+          <t>71683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44624</t>
+          <t>44893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60043</t>
+          <t>59964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42846</t>
+          <t>42081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57258</t>
+          <t>57264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92001</t>
+          <t>91761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112991</t>
+          <t>112855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,21%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32193</t>
+          <t>32174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47019</t>
+          <t>46797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27051</t>
+          <t>27581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40787</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63479</t>
+          <t>62955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83236</t>
+          <t>82831</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17838</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>26229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37484</t>
+          <t>37588</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29285</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41726</t>
+          <t>41065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59005</t>
+          <t>58748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75556</t>
+          <t>75837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>17795</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29376</t>
+          <t>29093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33094</t>
+          <t>32584</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48585</t>
+          <t>48732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34288</t>
+          <t>33978</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49073</t>
+          <t>49611</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47671</t>
+          <t>46733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62204</t>
+          <t>62249</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86664</t>
+          <t>85813</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107346</t>
+          <t>106731</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>21807</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36914</t>
+          <t>36723</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45093</t>
+          <t>44864</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65078</t>
+          <t>66025</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,02%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>133529</t>
+          <t>134832</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>161198</t>
+          <t>163562</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>161906</t>
+          <t>162688</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189519</t>
+          <t>190414</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>304489</t>
+          <t>303698</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>342651</t>
+          <t>342868</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>106096</t>
+          <t>103672</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>131644</t>
+          <t>132260</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>99791</t>
+          <t>99166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>126102</t>
+          <t>125817</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>213939</t>
+          <t>212815</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>251174</t>
+          <t>250509</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>21170</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26225</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,82 +3814,82 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>4460</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>8847</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>1245</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>4137</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>4460</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>9023</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32368</t>
+          <t>32357</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>44440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,49 +4389,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>70,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>44247</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>37508</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51138</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>61,47%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>52,11%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>71,05%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>44247</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>37067</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51528</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>61,47%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>51,5%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>71,59%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>114</t>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74539</t>
+          <t>73841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92811</t>
+          <t>91665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31249</t>
+          <t>31040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>36861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53552</t>
+          <t>55198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,76%</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49711</t>
+          <t>48990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64394</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47513</t>
+          <t>47033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62626</t>
+          <t>62377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101857</t>
+          <t>100792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123823</t>
+          <t>121826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24402</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24532</t>
+          <t>24451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39018</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52027</t>
+          <t>52630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72664</t>
+          <t>72366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31203</t>
+          <t>31850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43878</t>
+          <t>43913</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43867</t>
+          <t>44359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55780</t>
+          <t>55776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79890</t>
+          <t>80032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96368</t>
+          <t>96587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15412</t>
+          <t>15575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>27406</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28497</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44315</t>
+          <t>43749</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38783</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53794</t>
+          <t>54978</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>50340</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64945</t>
+          <t>65157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93854</t>
+          <t>93206</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115823</t>
+          <t>116329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,25%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22925</t>
+          <t>22840</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38490</t>
+          <t>37543</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20965</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34994</t>
+          <t>35762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49100</t>
+          <t>47189</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>69421</t>
+          <t>68776</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19638</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>166825</t>
+          <t>165546</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>195940</t>
+          <t>194972</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>194093</t>
+          <t>192686</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>223353</t>
+          <t>220965</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>367535</t>
+          <t>369661</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>410143</t>
+          <t>410537</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>88910</t>
+          <t>89774</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>117377</t>
+          <t>116250</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83841</t>
+          <t>85188</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>111232</t>
+          <t>112198</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>179967</t>
+          <t>178860</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>219754</t>
+          <t>218754</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>20327</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25944</t>
+          <t>26844</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45508</t>
+          <t>45731</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33839</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47945</t>
+          <t>47295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34066</t>
+          <t>33841</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>48263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71996</t>
+          <t>72613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92951</t>
+          <t>93214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18510</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29467</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37519</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57154</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>46307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62571</t>
+          <t>61642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53724</t>
+          <t>54398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70539</t>
+          <t>70463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104580</t>
+          <t>105350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128148</t>
+          <t>127802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31131</t>
+          <t>32168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46046</t>
+          <t>46910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24219</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39632</t>
+          <t>39117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58935</t>
+          <t>59469</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81738</t>
+          <t>81413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,69%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9212</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>555</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37954</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51625</t>
+          <t>51450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42243</t>
+          <t>42596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56226</t>
+          <t>56329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86360</t>
+          <t>85840</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104086</t>
+          <t>104647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,41%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25954</t>
+          <t>24776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15789</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29225</t>
+          <t>28773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32373</t>
+          <t>31881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49722</t>
+          <t>49625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>766</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12491</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43792</t>
+          <t>43781</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61024</t>
+          <t>61091</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45137</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61712</t>
+          <t>62279</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95013</t>
+          <t>93267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119482</t>
+          <t>117622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31659</t>
+          <t>31209</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>49120</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32089</t>
+          <t>31790</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48001</t>
+          <t>48250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67725</t>
+          <t>68414</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>90928</t>
+          <t>93037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>14550</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18570</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178355</t>
+          <t>178210</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>208211</t>
+          <t>208269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>192947</t>
+          <t>193436</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>223949</t>
+          <t>225122</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>380049</t>
+          <t>380194</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>422422</t>
+          <t>424561</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,32%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107989</t>
+          <t>108685</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>136174</t>
+          <t>137970</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>99605</t>
+          <t>101107</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>129345</t>
+          <t>130178</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>217171</t>
+          <t>217140</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>259697</t>
+          <t>260226</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>30497</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32642</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53247</t>
+          <t>54780</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12548</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
